--- a/docs/oc-regiones/emergencias-contingencias-y-prevencion/region-de-la-araucania.xlsx
+++ b/docs/oc-regiones/emergencias-contingencias-y-prevencion/region-de-la-araucania.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2103-476-CM26</t>
+          <t>3516-28-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-01-16</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.607.402-4</t>
+          <t>69.190.500-4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hospital  Lonquimay</t>
+          <t>I MUNICIPALIDAD DE CARAHUE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>DIMERC S A</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>96.670.840-9</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>223.77</v>
+        <v>236.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3697-628-CM26</t>
+          <t>3516-65-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2025-01-24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.180.900-5</t>
+          <t>69.190.500-4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICTORIA</t>
+          <t>I MUNICIPALIDAD DE CARAHUE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5812.97</v>
+        <v>308.2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2736-272-CM26</t>
+          <t>2546-35-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2025-01-30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.180.100-4</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SODIMAC S.A.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>96.792.430-K</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>15017.62</v>
+        <v>3486.67</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2736-289-CM26</t>
+          <t>2546-74-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.180.100-4</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANGOL</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.566.610-4</t>
+          <t>76.148.628-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>18617.97</v>
+        <v>6859.72</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1658-2328-CM26</t>
+          <t>3153-40-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>69.190.700-7</t>
+          <t>69.180.500-k</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TEMUCO</t>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>GIOVANNI SEBASTIAN</t>
+          <t>FRANCISCO JAVIER GIACAMAN HASBUN CONFECCION Y BORDADOS EMPRESA INDIVID</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.737.293-0</t>
+          <t>76.238.721-2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1219.53</v>
+        <v>5813.34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4179-1010-CM26</t>
+          <t>1091-278-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.190.100-9</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAUTARO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>77.325.352-8</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3264.15</v>
+        <v>2124.44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2548-519-CM26</t>
+          <t>4284-231-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2025-05-29</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.191.000-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE CUNCO</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MUÑOZ Y VILCHES LIMITADA</t>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.008.207-2</t>
+          <t>78.094.280-0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,6 +935,1409 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
+        <v>1985.54</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2546-456-CM25</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025-06-10</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>COMERCIAL ORIONIS SPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>77.721.492-6</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>17778.44</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>3887-315-CM25</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>69.191.500-K</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VILLARRICA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Sociedad Distribuidora Las Pataguas Ltda.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>78.094.280-0</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>2177.19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>3153-215-CM25</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025-07-17</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>69.180.500-k</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL SERI SPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>76.148.628-4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>4865.95</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2036-376-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-07-21</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>61.602.247-4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DE LA ARAUCANIA SUR HOSPITAL LONCOCHE</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Hales Hnos y Cia Ltda</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>83.535.000-2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>1124.1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3935-114-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jul-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.190.900-K</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>GIORGIO STEFANO RATTO ANDAUR</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>15.775.663-k</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>12412.43</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>701426-262-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ago-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-08-19</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>69.180.500-k</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COLLIPULLI</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>COMERCIAL EL TORO SPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>76.209.677-3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>2438.22</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1079659-317-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-09-02</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.980.860-6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>2278.03</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>3565-579-CM25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-09-04</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.252.100-5</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD TEODORO SCHMIDT</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>4452.91</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1091-414-CM25</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025-09-12</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>2735.03</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2546-795-CM25</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025-09-22</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>COMERCIAL ORIONIS SPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>77.721.492-6</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>5142.74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3460-281-CM25</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025-09-25</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.101.069-9</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>5006.98</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>3890-329-CM25</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.190.900-K</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SERVICIO Y COMERCIALIZADORA RAG SUR SPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>76.141.693-6</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>1302.66</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>3935-179-CM25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.190.900-K</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SERVICIO Y COMERCIALIZADORA RAG SUR SPA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>76.141.693-6</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>11205.43</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>3460-320-CM25</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025-10-24</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>61.101.069-9</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SERVICIOS INTEGRADOS SIDAPT LIMITADA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>76.299.358-9</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>6425.89</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>3935-198-CM25</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025-10-27</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.190.900-K</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>11108.77</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2546-908-CM25</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>KATHERINE LORENA ZAMORANO LOPEZ</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>15.888.842-4</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>14922.27</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2103-476-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>61.607.402-4</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Hospital  Lonquimay</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>DIMERC S A</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>96.670.840-9</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>223.77</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>3697-628-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.180.900-5</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VICTORIA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>5812.97</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2736-272-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>69.180.100-4</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>15017.62</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2736-289-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>69.180.100-4</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ANGOL</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>CONSULTORA SERGIO CACERES E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.566.610-4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>18617.97</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1658-2328-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>69.190.700-7</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TEMUCO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>GIOVANNI SEBASTIAN</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.737.293-0</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>1219.53</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>4179-1010-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>69.190.100-9</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE LAUTARO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>CONFECCIONES Y BORDADOS MONICA SABAL PICHARA SPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>77.325.352-8</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>3264.15</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2548-519-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-8-LR24</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>61.955.000-5</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de la Araucanía </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>MUÑOZ Y VILCHES LIMITADA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>77.008.207-2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
         <v>559.36</v>
       </c>
     </row>
